--- a/final/data_quality_analysis.xlsx
+++ b/final/data_quality_analysis.xlsx
@@ -42034,15 +42034,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="84" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -42140,739 +42140,5281 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>772885082</t>
+        </is>
+      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Two unfinished structures</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: ground</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>772885082</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2 roomed house-no information</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 1 room wooden cabin</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Cottage three roomed-Unavailable no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 1 room wooden cabin</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Cottage 3 roomed fenced and a wooden cabin</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: UN occupied</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Unfinished structure</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 1 room</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>No details 2396</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>3 roomed cottage,no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>No details 2396</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3 roomed cottage,no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>No details 2386</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>1 room no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details 2386</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>0771030120</t>
-        </is>
-      </c>
+      <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Wooden Cabin,unoccupied</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 4 roomed cottage</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>No details 2786</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Unfinished Structure</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details 2786</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>No details 2685</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Unfinished structure</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details 2685</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>No details</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>No one present ,3 roomed house</t>
+          <t>Size: 300, Lot: 143, Paid: 0.0, Bal: 0.0, Notes: 1   room cottage</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>No one present ,5 roomed house</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 1 room wooden cabin</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>No details 2684</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>4 roomed house and unfinished structure</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Two roomed cottage</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details 2682</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>No one present ,2 roomed houses</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure no detail...</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>No details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: ground</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details 2678</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>0779349061</t>
-        </is>
-      </c>
+      <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>No details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Three roomed cottage no detail...</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>No details 2715</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Unfinished structure-no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>0783957571</t>
-        </is>
-      </c>
+      <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1 roomed cottage ,no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: UN occupied</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>4 roomd cottage ,no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: unfinished structure</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>07731043889</t>
-        </is>
-      </c>
+      <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>1 roomed cottage ,no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 1 room wooden cabin</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>772974737</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2 roomed cottage,no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed unfinished structure ...</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="inlineStr"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>2 roomed cottage,no details</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed unfinished structure</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>[No Name Captured]</t>
+          <t>no details</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Wooden Cabin,foundation main house</t>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3roomed unfinished structure</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>batch_tat_300.csv</t>
+          <t>batch_tablet_300.csv</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>775189062</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2666</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 1, Paid: 0.0, Bal: 0.0, Notes: 3 roomed cottage</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: wooden cabin</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 1 room wooden  cabin</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2658</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: ground</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2741</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed,house No details</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin, No details</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin, No details</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 4 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin, No details</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2595</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>263775070962</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed cottage..We need to c...</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2596</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied Someone claimed to ...</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: One roomed house,No details</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2592</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>775960509</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed cottage, no agreement...</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2589</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Unoccupied 2589</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied stand, no structure</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>No details 2588</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed cottage, No details, ...</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure no detail...</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>No details 2584</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure full hous...</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>No details 2582</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>263714650292</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed cottage, Need to cont...</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>No details 2406</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure. no detai...</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>No details 2404</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details, Unoccupied stand.</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: 0.0, Bal: 0.0, Notes: 1 room wooden cabin</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: 0.0, Bal: 0.0, Notes: unfinished structure</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3roomed cottage</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2415</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: unfinished structure</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2417</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>773831214</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: 0.0, Bal: 0.0, Notes: 3roomed cottage</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>772808337</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed cottage</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3roomed cottage</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2426</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed cottage</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2427</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: UN occupied ground</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2364</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure, No detai...</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Box, No details</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2365</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 4 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2369</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin, No agreement of ...</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2374</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied, No details</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2384</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2373</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied, Fenced</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure,No detail...</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house , No details</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Built box,No details</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2255</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>No details 2255</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr"/>
+      <c r="D75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: one room cottage  no agreement...</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2254</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>No details 2254</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>263787592949</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: one room  cottage</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2241</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: unfinished structure</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 1 room finished and 2 unfinish...</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2206</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed cottage</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2191</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>No details 2191</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>2191</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>263775729823</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: there is a foundation .... Uno...</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>No details 2192</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
+      <c r="D81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Two roomed cottage no details</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2247</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2219</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 1 roomed house</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr"/>
+      <c r="D85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure, No detai...</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure, No detai...</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2251</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr"/>
+      <c r="D87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied, Bricks and well av...</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr"/>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin, No details</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>No details 2187</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr"/>
+      <c r="D89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied stand</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>No details 2186</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: full house (five roomed house)...</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>no details 2163</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: no details Unoccupied stand</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2170</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: $0.00, Bal: 0.0, Notes: unfinished structure</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2168</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr"/>
+      <c r="D93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: $0.00, Bal: 0.0, Notes: 1 room wooden cabin</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>2157</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>No details 2157</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr"/>
+      <c r="D94" s="3" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details 2 roomed cottage</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2156</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>No details 2156</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr"/>
+      <c r="D95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Full house (5rooms) no details...</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2846</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14/, Paid: 0.0, Bal: 0.0</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2843</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>no details 2843</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr"/>
+      <c r="D98" s="3" t="inlineStr"/>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: unfinished structure</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>No details 2838</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr"/>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>263771229277</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: one room we need to contact he...</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2865</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr"/>
+      <c r="D100" s="3" t="inlineStr"/>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure,No detail...</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2862</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr"/>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>772527090</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house, No agreement o...</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2868</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr"/>
+      <c r="D102" s="3" t="inlineStr"/>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr"/>
+      <c r="D103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure, No detai...</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2853</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr"/>
+      <c r="D104" s="3" t="inlineStr"/>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: One roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr"/>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>778368608</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: 0.0, Bal: 0.0, Notes: 3 roomed wooden cabin</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr"/>
+      <c r="D106" s="3" t="inlineStr"/>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2863</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr"/>
+      <c r="D107" s="4" t="inlineStr"/>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: One roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2860</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr"/>
+      <c r="D108" s="3" t="inlineStr"/>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed wooden cabin, No deta...</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr"/>
+      <c r="D109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 4 roomed house,No details</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2867</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr"/>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>773983490</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: No details</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr"/>
+      <c r="D111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>No cabin</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr"/>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr"/>
+      <c r="D113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: no structure</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>No details 2500</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr"/>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Ground No structure</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2506</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>No details 2506</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr"/>
+      <c r="D115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure...No deta...</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr"/>
+      <c r="D116" s="3" t="inlineStr"/>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house, No one availab...</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2466</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr"/>
+      <c r="D117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr"/>
+      <c r="D118" s="3" t="inlineStr"/>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 4 roomed house, Durawall, No d...</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr"/>
+      <c r="D119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin, Unoccupied</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr"/>
+      <c r="D120" s="3" t="inlineStr"/>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 4 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr"/>
+      <c r="D121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>2468</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr"/>
+      <c r="D122" s="3" t="inlineStr"/>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr"/>
+      <c r="D123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>2458</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr"/>
+      <c r="D124" s="3" t="inlineStr"/>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed house, Durawall ,No d...</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr"/>
+      <c r="D125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed house,No details</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr"/>
+      <c r="D126" s="3" t="inlineStr"/>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2477</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr"/>
+      <c r="D127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin, Unoccupied</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>2562</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr"/>
+      <c r="D128" s="3" t="inlineStr"/>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr"/>
+      <c r="D129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 2 roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>2475</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr"/>
+      <c r="D130" s="3" t="inlineStr"/>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed house</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2480</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr"/>
+      <c r="D131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>2470</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr"/>
+      <c r="D132" s="3" t="inlineStr"/>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unfinished structure</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2469</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr"/>
+      <c r="D133" s="4" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin,</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2473</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr"/>
+      <c r="D134" s="3" t="inlineStr"/>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied, Bricks present</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr"/>
+      <c r="D135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Unoccupied</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr"/>
+      <c r="D136" s="3" t="inlineStr"/>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: One roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr"/>
+      <c r="D137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: One roomed house, No details</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>2515</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr"/>
+      <c r="D138" s="3" t="inlineStr"/>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed house</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr"/>
+      <c r="D139" s="4" t="inlineStr"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: 3 roomed house,No one availabl...</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Nodetails</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr"/>
+      <c r="D140" s="3" t="inlineStr"/>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Wooden cabin</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr"/>
+      <c r="D141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: 0.0, Bal: 0.0, Notes: 1 room no details</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr"/>
+      <c r="D142" s="3" t="inlineStr"/>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Size: 300, Paid: 0.0, Bal: 0.0, Notes: no Details</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_300.csv</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2697</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr"/>
+      <c r="D143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: 1 room no details</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>2683</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>no details 2683</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr"/>
+      <c r="D144" s="3" t="inlineStr"/>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: foundation of full house no de...</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr"/>
+      <c r="D145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: 1 roomed cottage no details</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>2694</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr"/>
+      <c r="D146" s="3" t="inlineStr"/>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: 2 roomed cottage no details</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr"/>
+      <c r="D147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: 3 roomed house no details</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>No details 2400</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr"/>
+      <c r="D148" s="3" t="inlineStr"/>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: No details</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>no details</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr"/>
+      <c r="D149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>Size: 2845, Lot: 14, Paid: 0.0, Bal: 0.0</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>No details 2498</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr"/>
+      <c r="D150" s="3" t="inlineStr"/>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Lot: 14, Paid: 0.0, Bal: 0.0, Notes: Ground</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2531</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr"/>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>784175777</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: ground no details</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>2526</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr"/>
+      <c r="D152" s="3" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: ground no details</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>2532</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr"/>
+      <c r="D153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: ground no details</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>2533</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr"/>
+      <c r="D154" s="3" t="inlineStr"/>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: 2 rooms cottage no details</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>nodeals</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr"/>
+      <c r="D155" s="4" t="inlineStr"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: 4 roomed cottage no details</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>2548</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr"/>
+      <c r="D156" s="3" t="inlineStr"/>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: no information</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>2547</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>nodetails</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr"/>
+      <c r="D157" s="4" t="inlineStr"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>Paid: 0.0, Bal: 0.0, Notes: no information</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>batch_tablet_non_standard.csv</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr"/>
+      <c r="D158" s="3" t="inlineStr"/>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Two unfinished structures</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>2572</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr"/>
+      <c r="D159" s="4" t="inlineStr"/>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>2 roomed house-no information</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>2574</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr"/>
+      <c r="D160" s="3" t="inlineStr"/>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>Cottage three roomed-Unavailable no details</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>2575</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr"/>
+      <c r="D161" s="4" t="inlineStr"/>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Cottage 3 roomed fenced and a wooden cabin</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>2576</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr"/>
+      <c r="D162" s="3" t="inlineStr"/>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Unfinished structure</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr"/>
+      <c r="D163" s="4" t="inlineStr"/>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>3 roomed cottage,no details</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>2628</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr"/>
+      <c r="D164" s="3" t="inlineStr"/>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>3 roomed cottage,no details</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr"/>
+      <c r="D165" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>1 room no details</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr"/>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>0771030120</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Wooden Cabin,unoccupied</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>2444</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr"/>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Unfinished Structure</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr"/>
+      <c r="D168" s="3" t="inlineStr"/>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Unfinished structure</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr"/>
+      <c r="D169" s="4" t="inlineStr"/>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>No one present ,3 roomed house</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>2452</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr"/>
+      <c r="D170" s="3" t="inlineStr"/>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>No one present ,5 roomed house</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr"/>
+      <c r="D171" s="4" t="inlineStr"/>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>4 roomed house and unfinished structure</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr"/>
+      <c r="D172" s="3" t="inlineStr"/>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>No one present ,2 roomed houses</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr"/>
+      <c r="D173" s="4" t="inlineStr"/>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr"/>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>0779349061</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>No details</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr"/>
+      <c r="D175" s="4" t="inlineStr"/>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>Unfinished structure-no details</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr"/>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>0783957571</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>1 roomed cottage ,no details</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr"/>
+      <c r="D177" s="4" t="inlineStr"/>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>4 roomd cottage ,no details</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>2908</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr"/>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>07731043889</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>1 roomed cottage ,no details</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>2912</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr"/>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>2 roomed cottage,no details</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>2913</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr"/>
+      <c r="D180" s="3" t="inlineStr"/>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>2 roomed cottage,no details</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>2894</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>[No Name Captured]</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr"/>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>Wooden Cabin,foundation main house</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>batch_tat_300.csv</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
           <t>2893</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>[No Name Captured]</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr"/>
+      <c r="D182" s="3" t="inlineStr"/>
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>3 roomed house,tenant (No details)</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr">
         <is>
           <t>batch_tat_300.csv</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G182" s="3" t="inlineStr">
         <is>
           <t>153</t>
         </is>
